--- a/графики/Заказы на 26-27 НВ КИ.xlsx
+++ b/графики/Заказы на 26-27 НВ КИ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7D1F0F-4E09-4619-A49D-C9C03CB6CE8F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670E6089-9DFC-4F40-9527-FD294C9FF96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,23 +16,17 @@
     <sheet name="КИ" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="77">
   <si>
     <t>Заказ</t>
   </si>
@@ -260,13 +254,16 @@
   </si>
   <si>
     <t>TSO001127083</t>
+  </si>
+  <si>
+    <t>ДОЗАКАЗ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,8 +440,16 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,6 +650,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1124,11 +1135,10 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="42" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="42" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="42" applyBorder="1"/>
     <xf numFmtId="4" fontId="18" fillId="0" borderId="10" xfId="42" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="42" applyFill="1" applyBorder="1"/>
@@ -1141,9 +1151,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="42" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="42" applyBorder="1"/>
@@ -1164,7 +1171,7 @@
     <xf numFmtId="4" fontId="18" fillId="0" borderId="24" xfId="42" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="24" xfId="42" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="24" xfId="42" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="42" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="42" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="42" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
@@ -1172,7 +1179,7 @@
     <xf numFmtId="4" fontId="18" fillId="0" borderId="29" xfId="42" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="29" xfId="42" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="29" xfId="42" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="42" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="42" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="24" xfId="42" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
@@ -1183,17 +1190,22 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="42" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="42" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="35" borderId="28" xfId="42" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="42" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="42" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="35" borderId="31" xfId="42" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="19" xfId="42" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="35" xfId="42" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="35" xfId="42" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="35" borderId="23" xfId="42" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" xfId="42" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="22" xfId="42" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="12" xfId="42" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="21" fillId="37" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="21" fillId="37" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1203,7 +1215,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1212,7 +1224,7 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="42" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="22" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1230,7 +1242,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="42" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="22" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1558,7 +1570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.140625" customWidth="1"/>
@@ -1576,974 +1588,1027 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="15">
         <v>16833.14</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="16">
         <v>4124407.95</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="18">
         <v>46290</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="P2" s="22">
+      <c r="P2" s="20">
         <v>22.09</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="23">
+      <c r="B3" s="78"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="21">
         <f>SUM(D2)</f>
         <v>16833.14</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="27">
         <v>14922.56</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="28">
         <v>3808639.15</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="30">
         <v>46290</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="33" t="s">
+      <c r="M4" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N4" s="63" t="s">
+      <c r="N4" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="O4" s="63" t="s">
+      <c r="O4" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="32">
         <v>21.09</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="35">
         <v>1905</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="36">
         <v>304648.95</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="39" t="s">
+      <c r="G5" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="40">
+      <c r="H5" s="38">
         <v>46290</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="37" t="s">
+      <c r="K5" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="41" t="s">
+      <c r="M5" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="N5" s="64"/>
-      <c r="O5" s="64"/>
-      <c r="P5" s="42">
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="40">
         <v>21.09</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="75"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="23">
+      <c r="B6" s="78"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="21">
         <f>SUM(D4:D5)</f>
         <v>16827.559999999998</v>
       </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="27">
         <v>8135.28</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="28">
         <v>1957741.51</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="G7" s="43" t="s">
+      <c r="G7" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="30">
         <v>46291</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="J7" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="33" t="s">
+      <c r="M7" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="34">
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="32">
         <v>26.09</v>
       </c>
-      <c r="Q7" s="62">
+      <c r="Q7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>917.64</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8" t="s">
+      <c r="E8" s="8"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="11" t="s">
+      <c r="H8" s="9"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="46">
+      <c r="P8" s="44">
         <v>26.09</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="35">
         <v>8643.5400000000009</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="36">
         <v>2186079.06</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="G9" s="47" t="s">
+      <c r="G9" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="40">
+      <c r="H9" s="38">
         <v>46291</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="37" t="s">
+      <c r="J9" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="M9" s="41" t="s">
+      <c r="M9" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="48"/>
-      <c r="O9" s="48"/>
-      <c r="P9" s="42">
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="40">
         <v>26.09</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="68" t="s">
+    <row r="10" spans="1:17" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="60"/>
+      <c r="C10" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="62">
+        <v>960</v>
+      </c>
+      <c r="E10" s="63"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
+      <c r="M10" s="60"/>
+    </row>
+    <row r="11" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="69"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="49">
-        <f>SUM(D7:D9)</f>
-        <v>17696.46</v>
-      </c>
-      <c r="E10" s="24"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="B11" s="72"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="47">
+        <f>SUM(D7:D10)</f>
+        <v>18656.46</v>
+      </c>
+      <c r="E11" s="22"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B12" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C12" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D12" s="27">
         <v>2218.1999999999998</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E12" s="28">
         <v>524159.06</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F12" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="G11" s="43" t="s">
+      <c r="G12" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H12" s="30">
         <v>46291</v>
       </c>
-      <c r="I11" s="29" t="s">
+      <c r="I12" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="29" t="s">
+      <c r="J12" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="29" t="s">
+      <c r="K12" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="L11" s="29" t="s">
+      <c r="L12" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="M11" s="33" t="s">
+      <c r="M12" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="N11" s="44"/>
-      <c r="O11" s="65" t="s">
+      <c r="N12" s="42"/>
+      <c r="O12" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="P11" s="34">
+      <c r="P12" s="32">
         <v>26.09</v>
       </c>
-      <c r="Q11">
+      <c r="Q12">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="50" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D13" s="3">
         <v>10534.85</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E13" s="4">
         <v>2469301.84</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H13" s="6">
         <v>46291</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="46">
+      <c r="O13" s="69"/>
+      <c r="P13" s="44">
         <v>26.09</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D14" s="3">
         <v>920.1</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="52" t="s">
+      <c r="E14" s="4"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="66"/>
-      <c r="P13" s="46">
+      <c r="O14" s="69"/>
+      <c r="P14" s="44">
         <v>26.09</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="51" t="s">
+    <row r="15" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B15" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C15" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="37">
+      <c r="D15" s="35">
         <v>3755.04</v>
       </c>
-      <c r="E14" s="38"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37"/>
-      <c r="M14" s="53" t="s">
+      <c r="E15" s="36"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="N14" s="48"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="42">
+      <c r="N15" s="46"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="40">
         <v>27.09</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="68" t="s">
+    <row r="16" spans="1:17" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="60"/>
+      <c r="C16" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="62">
+        <v>810</v>
+      </c>
+      <c r="E16" s="63"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="62"/>
+      <c r="M16" s="60"/>
+    </row>
+    <row r="17" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="69"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="49">
-        <f>SUM(D11:D14)</f>
-        <v>17428.189999999999</v>
-      </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-    </row>
-    <row r="16" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+      <c r="B17" s="72"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="47">
+        <f>SUM(D12:D16)</f>
+        <v>18238.189999999999</v>
+      </c>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+    </row>
+    <row r="18" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B18" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D18" s="15">
         <v>17596.78</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E18" s="16">
         <v>3874349.11</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F18" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="G16" s="54" t="s">
+      <c r="G18" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H18" s="18">
         <v>46292</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="J16" s="17" t="s">
+      <c r="J18" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="K16" s="17" t="s">
+      <c r="K18" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="17" t="s">
+      <c r="L18" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="M16" s="55" t="s">
+      <c r="M18" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="22">
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="20">
         <v>27.09</v>
       </c>
-      <c r="Q16" s="61">
+      <c r="Q18" s="59">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="68" t="s">
+    <row r="19" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="49">
-        <f>SUM(D16)</f>
+      <c r="B19" s="72"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="47">
+        <f>SUM(D18)</f>
         <v>17596.78</v>
       </c>
-      <c r="E17" s="24"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="Q17" s="62"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="E19" s="22"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B20" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C20" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D20" s="27">
         <v>13916.16</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E20" s="28">
         <v>3131303.19</v>
       </c>
-      <c r="F18" s="29" t="s">
+      <c r="F20" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="43" t="s">
+      <c r="G20" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="32">
+      <c r="H20" s="30">
         <v>46292</v>
       </c>
-      <c r="I18" s="29" t="s">
+      <c r="I20" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="J18" s="29" t="s">
+      <c r="J20" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="L18" s="29" t="s">
+      <c r="L20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="M18" s="33" t="s">
+      <c r="M20" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="N18" s="44"/>
-      <c r="O18" s="44"/>
-      <c r="P18" s="34">
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="32">
         <v>27.09</v>
       </c>
-      <c r="Q18" s="62">
+      <c r="Q20">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="35" t="s">
+    <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B21" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C21" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D21" s="35">
         <v>3931.3</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E21" s="36">
         <v>984233.1</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F21" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="47" t="s">
+      <c r="G21" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="40">
+      <c r="H21" s="38">
         <v>46292</v>
       </c>
-      <c r="I19" s="37" t="s">
+      <c r="I21" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="J19" s="37" t="s">
+      <c r="J21" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="K19" s="37" t="s">
+      <c r="K21" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="L19" s="37" t="s">
+      <c r="L21" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="M19" s="41" t="s">
+      <c r="M21" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="42">
+      <c r="N21" s="46"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="40">
         <v>27.09</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="68" t="s">
+    <row r="22" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="69"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="49">
-        <f>SUM(D18:D19)</f>
+      <c r="B22" s="72"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="47">
+        <f>SUM(D20:D21)</f>
         <v>17847.46</v>
       </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="57" t="s">
+      <c r="E22" s="22"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B23" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C23" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D23" s="27">
         <v>2503.7999999999997</v>
       </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="58" t="s">
+      <c r="E23" s="28"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="34">
+      <c r="N23" s="42"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="32">
         <v>26.09</v>
       </c>
-      <c r="Q21" s="61">
+      <c r="Q23" s="59">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="45" t="s">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D24" s="3">
         <v>5722.3</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="59" t="s">
+      <c r="E24" s="4"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="46">
+      <c r="P24" s="44">
         <v>26.09</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="35" t="s">
+    <row r="25" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="37" t="s">
+      <c r="B25" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C25" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="37">
+      <c r="D25" s="35">
         <v>9399.86</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E25" s="36">
         <v>2341273</v>
       </c>
-      <c r="F23" s="37" t="s">
+      <c r="F25" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="G23" s="47" t="s">
+      <c r="G25" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="40">
+      <c r="H25" s="38">
         <v>46291</v>
       </c>
-      <c r="I23" s="37" t="s">
+      <c r="I25" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="37" t="s">
+      <c r="J25" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="K23" s="37" t="s">
+      <c r="K25" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="L23" s="37" t="s">
+      <c r="L25" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="M23" s="48" t="s">
+      <c r="M25" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="N23" s="48"/>
-      <c r="O23" s="48"/>
-      <c r="P23" s="42">
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="40">
         <v>26.09</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="68" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="69"/>
-      <c r="C24" s="70"/>
-      <c r="D24" s="1">
-        <f>SUM(D21:D23)</f>
-        <v>17625.96</v>
-      </c>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="60"/>
-      <c r="J24" s="60"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="60"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="57" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="29">
-        <v>12165.6</v>
-      </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="N25" s="44"/>
-      <c r="O25" s="44"/>
-      <c r="P25" s="34">
-        <v>27.09</v>
-      </c>
-      <c r="Q25">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="37">
-        <v>5466.94</v>
-      </c>
-      <c r="E26" s="38">
-        <v>1326191.97</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="40">
-        <v>46292</v>
-      </c>
-      <c r="I26" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="K26" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="L26" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="M26" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48"/>
-      <c r="P26" s="42">
-        <v>27.09</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="60"/>
+      <c r="C26" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="62">
+        <v>600</v>
+      </c>
+      <c r="E26" s="63"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="62"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="60"/>
+    </row>
+    <row r="27" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="71" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="72"/>
       <c r="C27" s="73"/>
       <c r="D27" s="1">
-        <f>SUM(D25:D26)</f>
+        <f>SUM(D23:D26)</f>
+        <v>18225.96</v>
+      </c>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="58"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="27">
+        <v>12165.6</v>
+      </c>
+      <c r="E28" s="28"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="N28" s="42"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="32">
+        <v>27.09</v>
+      </c>
+      <c r="Q28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="35">
+        <v>5466.94</v>
+      </c>
+      <c r="E29" s="36">
+        <v>1326191.97</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" s="38">
+        <v>46292</v>
+      </c>
+      <c r="I29" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="L29" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="M29" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="40">
+        <v>27.09</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="75"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="1">
+        <f>SUM(D28:D29)</f>
         <v>17632.54</v>
       </c>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="O4:O5"/>
-    <mergeCell ref="O11:O14"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="O12:O15"/>
     <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
